--- a/schwabAPI/data/transactions/0422CE2E96848FDF660FC4C76F25CC63FD00526DE42E04C27E5D70E493176FD3.xlsx
+++ b/schwabAPI/data/transactions/0422CE2E96848FDF660FC4C76F25CC63FD00526DE42E04C27E5D70E493176FD3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\rchak007\github\myTrading\schwabAPI\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3FE37887-78CF-4551-B1FE-CEEFECDA2FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8E9DCB-C24B-44CC-B905-50DFA32B5624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0416F62A-67BF-4CAB-BBF9-B684C68B891F}"/>
   </bookViews>
@@ -1762,11 +1762,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D08F2675-AFF5-4BC4-8A45-9611FEC249CE}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I236"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="69.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -1805,24 +1804,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="1">
-        <v>45551</v>
+        <v>45545</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1835,11 +1837,8 @@
       <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
-        <v>278</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>14</v>
+      <c r="I3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1847,50 +1846,44 @@
         <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>45545</v>
+        <v>45551</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="1">
-        <v>45622</v>
+        <v>45575</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="1">
-        <v>45622</v>
+        <v>45575</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1898,13 +1891,13 @@
         <v>8</v>
       </c>
       <c r="C7" s="1">
-        <v>45621</v>
+        <v>45575</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1912,64 +1905,61 @@
         <v>8</v>
       </c>
       <c r="C8" s="1">
-        <v>45621</v>
+        <v>45575</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="1">
-        <v>45614</v>
+        <v>45575</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="1">
-        <v>45593</v>
+        <v>45576</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="1">
-        <v>45593</v>
+        <v>45576</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1977,47 +1967,41 @@
         <v>8</v>
       </c>
       <c r="C12" s="1">
-        <v>45590</v>
+        <v>45580</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="I12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="1">
-        <v>45582</v>
+        <v>45581</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="1">
-        <v>45582</v>
+        <v>45581</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2031,7 +2015,7 @@
         <v>12</v>
       </c>
       <c r="I15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2042,10 +2026,13 @@
         <v>45581</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>33</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -2056,13 +2043,16 @@
         <v>45581</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -2070,47 +2060,47 @@
         <v>45581</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="1">
-        <v>45581</v>
+        <v>45582</v>
       </c>
       <c r="D19" t="s">
         <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="1">
-        <v>45581</v>
+        <v>45582</v>
       </c>
       <c r="D20" t="s">
         <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -2118,47 +2108,47 @@
         <v>8</v>
       </c>
       <c r="C21" s="1">
-        <v>45580</v>
+        <v>45590</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="I21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="1">
-        <v>45576</v>
+        <v>45593</v>
       </c>
       <c r="D22" t="s">
         <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="1">
-        <v>45576</v>
+        <v>45593</v>
       </c>
       <c r="D23" t="s">
         <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I23" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -2166,13 +2156,16 @@
         <v>8</v>
       </c>
       <c r="C24" s="1">
-        <v>45575</v>
+        <v>45614</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>23</v>
       </c>
       <c r="I24" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -2180,13 +2173,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="1">
-        <v>45575</v>
+        <v>45621</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="I25" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -2194,13 +2187,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="1">
-        <v>45575</v>
+        <v>45621</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
       <c r="I26" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -2208,13 +2201,16 @@
         <v>8</v>
       </c>
       <c r="C27" s="1">
-        <v>45575</v>
+        <v>45622</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F27" t="s">
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -2222,112 +2218,115 @@
         <v>8</v>
       </c>
       <c r="C28" s="1">
-        <v>45575</v>
+        <v>45622</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F28" t="s">
+        <v>19</v>
       </c>
       <c r="I28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="1">
-        <v>45673</v>
+        <v>45642</v>
       </c>
       <c r="D29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="1">
-        <v>45672</v>
+        <v>45649</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="1">
+        <v>45649</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" t="s">
+        <v>278</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="1">
+        <v>45649</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" t="s">
+        <v>278</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="1">
+        <v>45650</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" t="s">
         <v>17</v>
       </c>
-      <c r="I30" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="1">
-        <v>45672</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="I33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1">
+        <v>45650</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" t="s">
         <v>19</v>
       </c>
-      <c r="I31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="1">
-        <v>45671</v>
-      </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
-      <c r="I32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="1">
-        <v>45659</v>
-      </c>
-      <c r="D33" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" t="s">
-        <v>35</v>
-      </c>
-      <c r="I33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="1">
-        <v>45659</v>
-      </c>
-      <c r="D34" t="s">
-        <v>16</v>
-      </c>
-      <c r="F34" t="s">
-        <v>37</v>
-      </c>
       <c r="I34" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -2344,38 +2343,38 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="1">
-        <v>45650</v>
+        <v>45659</v>
       </c>
       <c r="D36" t="s">
         <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="1">
-        <v>45650</v>
+        <v>45659</v>
       </c>
       <c r="D37" t="s">
         <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2383,72 +2382,72 @@
         <v>8</v>
       </c>
       <c r="C38" s="1">
-        <v>45649</v>
+        <v>45671</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="I38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="1">
-        <v>45649</v>
+        <v>45672</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" t="s">
-        <v>278</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F39" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="1">
-        <v>45649</v>
+        <v>45672</v>
       </c>
       <c r="D40" t="s">
-        <v>12</v>
-      </c>
-      <c r="H40" t="s">
-        <v>278</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F40" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="1">
-        <v>45642</v>
+        <v>45673</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="I41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="1">
-        <v>45748</v>
+        <v>45691</v>
       </c>
       <c r="D42" t="s">
         <v>16</v>
@@ -2457,15 +2456,15 @@
         <v>19</v>
       </c>
       <c r="I42" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="1">
-        <v>45748</v>
+        <v>45691</v>
       </c>
       <c r="D43" t="s">
         <v>16</v>
@@ -2474,72 +2473,75 @@
         <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="1">
-        <v>45748</v>
+        <v>45691</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>64</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="I44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="1">
-        <v>45748</v>
+        <v>45694</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
-      </c>
-      <c r="F45" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H45" t="s">
+        <v>278</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="1">
-        <v>45748</v>
+        <v>45694</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
-      </c>
-      <c r="F46" t="s">
-        <v>19</v>
-      </c>
-      <c r="I46" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H46" t="s">
+        <v>279</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="1">
-        <v>45747</v>
+        <v>45694</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
-      <c r="I47" t="s">
-        <v>68</v>
+      <c r="H47" t="s">
+        <v>279</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -2547,282 +2549,285 @@
         <v>8</v>
       </c>
       <c r="C48" s="1">
-        <v>45747</v>
+        <v>45694</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
+      <c r="H48" t="s">
+        <v>279</v>
+      </c>
       <c r="I48" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="1">
-        <v>45744</v>
+        <v>45695</v>
       </c>
       <c r="D49" t="s">
         <v>16</v>
       </c>
       <c r="F49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="1">
+        <v>45695</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" t="s">
+        <v>37</v>
+      </c>
+      <c r="I50" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="1">
+        <v>45702</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="1">
+        <v>45702</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="1">
+        <v>45706</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" t="s">
+        <v>101</v>
+      </c>
+      <c r="I53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="1">
+        <v>45706</v>
+      </c>
+      <c r="D54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="1">
+        <v>45706</v>
+      </c>
+      <c r="D55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" t="s">
+        <v>37</v>
+      </c>
+      <c r="I55" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="1">
+        <v>45708</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" t="s">
+        <v>279</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="1">
+        <v>45708</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" t="s">
+        <v>278</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="1">
+        <v>45709</v>
+      </c>
+      <c r="D58" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="1">
+        <v>45709</v>
+      </c>
+      <c r="D59" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" t="s">
         <v>19</v>
       </c>
-      <c r="I49" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="1">
-        <v>45744</v>
-      </c>
-      <c r="D50" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I50" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="1">
-        <v>45744</v>
-      </c>
-      <c r="D51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>72</v>
-      </c>
-      <c r="I51" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="1">
-        <v>45741</v>
-      </c>
-      <c r="D52" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="I59" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="1">
+        <v>45712</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" t="s">
+        <v>279</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="1">
+        <v>45712</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="H61" t="s">
+        <v>279</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="1">
+        <v>45712</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" t="s">
+        <v>278</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="1">
+        <v>45713</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" t="s">
         <v>35</v>
       </c>
-      <c r="I52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="1">
-        <v>45741</v>
-      </c>
-      <c r="D53" t="s">
-        <v>16</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="I63" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="1">
+        <v>45713</v>
+      </c>
+      <c r="D64" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" t="s">
         <v>37</v>
       </c>
-      <c r="I53" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="1">
-        <v>45740</v>
-      </c>
-      <c r="D54" t="s">
-        <v>12</v>
-      </c>
-      <c r="H54" t="s">
-        <v>278</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="1">
-        <v>45740</v>
-      </c>
-      <c r="D55" t="s">
-        <v>12</v>
-      </c>
-      <c r="H55" t="s">
-        <v>279</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="1">
-        <v>45733</v>
-      </c>
-      <c r="D56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>78</v>
-      </c>
-      <c r="I56" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" s="1">
-        <v>45727</v>
-      </c>
-      <c r="D57" t="s">
-        <v>16</v>
-      </c>
-      <c r="F57" t="s">
-        <v>35</v>
-      </c>
-      <c r="I57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="1">
-        <v>45727</v>
-      </c>
-      <c r="D58" t="s">
-        <v>16</v>
-      </c>
-      <c r="F58" t="s">
-        <v>37</v>
-      </c>
-      <c r="I58" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" s="1">
-        <v>45726</v>
-      </c>
-      <c r="D59" t="s">
-        <v>12</v>
-      </c>
-      <c r="H59" t="s">
-        <v>279</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" s="1">
-        <v>45726</v>
-      </c>
-      <c r="D60" t="s">
-        <v>12</v>
-      </c>
-      <c r="I60" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" s="1">
-        <v>45726</v>
-      </c>
-      <c r="D61" t="s">
-        <v>12</v>
-      </c>
-      <c r="I61" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" s="1">
-        <v>45719</v>
-      </c>
-      <c r="D62" t="s">
-        <v>16</v>
-      </c>
-      <c r="F62" t="s">
-        <v>19</v>
-      </c>
-      <c r="I62" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="1">
-        <v>45719</v>
-      </c>
-      <c r="D63" t="s">
-        <v>16</v>
-      </c>
-      <c r="F63" t="s">
-        <v>17</v>
-      </c>
-      <c r="I63" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" s="1">
-        <v>45719</v>
-      </c>
-      <c r="D64" t="s">
-        <v>16</v>
-      </c>
-      <c r="F64" t="s">
-        <v>87</v>
-      </c>
       <c r="I64" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -2839,7 +2844,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -2856,7 +2861,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -2873,55 +2878,55 @@
         <v>91</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="1">
-        <v>45713</v>
+        <v>45719</v>
       </c>
       <c r="D68" t="s">
         <v>16</v>
       </c>
       <c r="F68" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I68" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="1">
-        <v>45713</v>
+        <v>45719</v>
       </c>
       <c r="D69" t="s">
         <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I69" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="1">
-        <v>45712</v>
+        <v>45719</v>
       </c>
       <c r="D70" t="s">
-        <v>12</v>
-      </c>
-      <c r="H70" t="s">
-        <v>279</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>94</v>
+        <v>16</v>
+      </c>
+      <c r="F70" t="s">
+        <v>87</v>
+      </c>
+      <c r="I70" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -2929,7 +2934,7 @@
         <v>8</v>
       </c>
       <c r="C71" s="1">
-        <v>45712</v>
+        <v>45726</v>
       </c>
       <c r="D71" t="s">
         <v>12</v>
@@ -2938,143 +2943,137 @@
         <v>279</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="1">
-        <v>45712</v>
+        <v>45726</v>
       </c>
       <c r="D72" t="s">
         <v>12</v>
       </c>
-      <c r="H72" t="s">
+      <c r="I72" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="1">
+        <v>45726</v>
+      </c>
+      <c r="D73" t="s">
+        <v>12</v>
+      </c>
+      <c r="I73" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="1">
+        <v>45727</v>
+      </c>
+      <c r="D74" t="s">
+        <v>16</v>
+      </c>
+      <c r="F74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="1">
+        <v>45727</v>
+      </c>
+      <c r="D75" t="s">
+        <v>16</v>
+      </c>
+      <c r="F75" t="s">
+        <v>37</v>
+      </c>
+      <c r="I75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="1">
+        <v>45733</v>
+      </c>
+      <c r="D76" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" t="s">
+        <v>78</v>
+      </c>
+      <c r="I76" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="1">
+        <v>45740</v>
+      </c>
+      <c r="D77" t="s">
+        <v>12</v>
+      </c>
+      <c r="H77" t="s">
         <v>278</v>
       </c>
-      <c r="I72" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" s="1">
-        <v>45709</v>
-      </c>
-      <c r="D73" t="s">
-        <v>16</v>
-      </c>
-      <c r="F73" t="s">
-        <v>17</v>
-      </c>
-      <c r="I73" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>8</v>
-      </c>
-      <c r="C74" s="1">
-        <v>45709</v>
-      </c>
-      <c r="D74" t="s">
-        <v>16</v>
-      </c>
-      <c r="F74" t="s">
-        <v>19</v>
-      </c>
-      <c r="I74" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>8</v>
-      </c>
-      <c r="C75" s="1">
-        <v>45708</v>
-      </c>
-      <c r="D75" t="s">
-        <v>12</v>
-      </c>
-      <c r="H75" t="s">
+      <c r="I77" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="1">
+        <v>45740</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="H78" t="s">
         <v>279</v>
       </c>
-      <c r="I75" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>8</v>
-      </c>
-      <c r="C76" s="1">
-        <v>45708</v>
-      </c>
-      <c r="D76" t="s">
-        <v>12</v>
-      </c>
-      <c r="H76" t="s">
-        <v>278</v>
-      </c>
-      <c r="I76" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>8</v>
-      </c>
-      <c r="C77" s="1">
-        <v>45706</v>
-      </c>
-      <c r="D77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" t="s">
-        <v>101</v>
-      </c>
-      <c r="I77" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>8</v>
-      </c>
-      <c r="C78" s="1">
-        <v>45706</v>
-      </c>
-      <c r="D78" t="s">
-        <v>16</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="I78" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="1">
+        <v>45741</v>
+      </c>
+      <c r="D79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" t="s">
         <v>35</v>
       </c>
-      <c r="I78" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>8</v>
-      </c>
-      <c r="C79" s="1">
-        <v>45706</v>
-      </c>
-      <c r="D79" t="s">
-        <v>16</v>
-      </c>
-      <c r="F79" t="s">
-        <v>37</v>
-      </c>
       <c r="I79" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -3082,13 +3081,16 @@
         <v>8</v>
       </c>
       <c r="C80" s="1">
-        <v>45702</v>
+        <v>45741</v>
       </c>
       <c r="D80" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F80" t="s">
+        <v>37</v>
       </c>
       <c r="I80" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -3096,64 +3098,64 @@
         <v>8</v>
       </c>
       <c r="C81" s="1">
-        <v>45702</v>
+        <v>45744</v>
       </c>
       <c r="D81" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F81" t="s">
+        <v>19</v>
       </c>
       <c r="I81" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="1">
-        <v>45695</v>
+        <v>45744</v>
       </c>
       <c r="D82" t="s">
         <v>16</v>
       </c>
       <c r="F82" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I82" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="1">
-        <v>45695</v>
+        <v>45744</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F83" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="I83" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="1">
-        <v>45694</v>
+        <v>45747</v>
       </c>
       <c r="D84" t="s">
         <v>12</v>
       </c>
-      <c r="H84" t="s">
-        <v>278</v>
-      </c>
-      <c r="I84" s="7" t="s">
-        <v>109</v>
+      <c r="I84" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -3161,75 +3163,72 @@
         <v>8</v>
       </c>
       <c r="C85" s="1">
-        <v>45694</v>
+        <v>45747</v>
       </c>
       <c r="D85" t="s">
         <v>12</v>
       </c>
-      <c r="H85" t="s">
-        <v>279</v>
-      </c>
       <c r="I85" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="1">
-        <v>45694</v>
+        <v>45748</v>
       </c>
       <c r="D86" t="s">
-        <v>12</v>
-      </c>
-      <c r="H86" t="s">
-        <v>279</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F86" t="s">
+        <v>19</v>
+      </c>
+      <c r="I86" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="1">
-        <v>45694</v>
+        <v>45748</v>
       </c>
       <c r="D87" t="s">
-        <v>12</v>
-      </c>
-      <c r="H87" t="s">
-        <v>279</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F87" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="1">
-        <v>45691</v>
+        <v>45748</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F88" t="s">
-        <v>19</v>
-      </c>
-      <c r="I88" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="1">
-        <v>45691</v>
+        <v>45748</v>
       </c>
       <c r="D89" t="s">
         <v>16</v>
@@ -3238,160 +3237,160 @@
         <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="1">
-        <v>45691</v>
+        <v>45748</v>
       </c>
       <c r="D90" t="s">
         <v>16</v>
       </c>
       <c r="F90" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="I90" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>8</v>
       </c>
       <c r="C91" s="1">
-        <v>45810</v>
+        <v>45756</v>
       </c>
       <c r="D91" t="s">
-        <v>12</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="F91" t="s">
+        <v>134</v>
+      </c>
+      <c r="I91" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="1">
-        <v>45807</v>
+        <v>45756</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="F92" t="s">
+        <v>136</v>
+      </c>
+      <c r="I92" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="1">
+        <v>45763</v>
+      </c>
+      <c r="D93" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" t="s">
+        <v>131</v>
+      </c>
+      <c r="I93" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="1">
+        <v>45776</v>
+      </c>
+      <c r="D94" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" t="s">
+        <v>17</v>
+      </c>
+      <c r="I94" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="1">
+        <v>45776</v>
+      </c>
+      <c r="D95" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95" t="s">
         <v>19</v>
       </c>
-      <c r="I92" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>8</v>
-      </c>
-      <c r="C93" s="1">
-        <v>45807</v>
-      </c>
-      <c r="D93" t="s">
-        <v>16</v>
-      </c>
-      <c r="F93" t="s">
-        <v>17</v>
-      </c>
-      <c r="I93" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94" s="1">
-        <v>45807</v>
-      </c>
-      <c r="D94" t="s">
-        <v>16</v>
-      </c>
-      <c r="F94" t="s">
-        <v>87</v>
-      </c>
-      <c r="I94" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>8</v>
-      </c>
-      <c r="C95" s="1">
-        <v>45806</v>
-      </c>
-      <c r="D95" t="s">
-        <v>16</v>
-      </c>
-      <c r="F95" t="s">
-        <v>17</v>
-      </c>
       <c r="I95" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="1">
-        <v>45806</v>
+        <v>45776</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="I96" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="1">
-        <v>45806</v>
+        <v>45791</v>
       </c>
       <c r="D97" t="s">
-        <v>9</v>
-      </c>
-      <c r="F97" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="I97" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="1">
-        <v>45793</v>
+        <v>45792</v>
       </c>
       <c r="D98" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -3402,27 +3401,27 @@
         <v>16</v>
       </c>
       <c r="F99" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I99" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>8</v>
       </c>
       <c r="C100" s="1">
-        <v>45792</v>
+        <v>45793</v>
       </c>
       <c r="D100" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F100" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="I100" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -3430,174 +3429,176 @@
         <v>8</v>
       </c>
       <c r="C101" s="1">
-        <v>45791</v>
+        <v>45806</v>
       </c>
       <c r="D101" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F101" t="s">
+        <v>17</v>
       </c>
       <c r="I101" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>8</v>
       </c>
       <c r="C102" s="1">
-        <v>45776</v>
+        <v>45806</v>
       </c>
       <c r="D102" t="s">
         <v>16</v>
       </c>
       <c r="F102" t="s">
+        <v>19</v>
+      </c>
+      <c r="I102" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="1">
+        <v>45806</v>
+      </c>
+      <c r="D103" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" t="s">
+        <v>72</v>
+      </c>
+      <c r="I103" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="1">
+        <v>45807</v>
+      </c>
+      <c r="D104" t="s">
+        <v>16</v>
+      </c>
+      <c r="F104" t="s">
+        <v>19</v>
+      </c>
+      <c r="I104" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>8</v>
+      </c>
+      <c r="C105" s="1">
+        <v>45807</v>
+      </c>
+      <c r="D105" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105" t="s">
         <v>17</v>
       </c>
-      <c r="I102" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>8</v>
-      </c>
-      <c r="C103" s="1">
-        <v>45776</v>
-      </c>
-      <c r="D103" t="s">
-        <v>16</v>
-      </c>
-      <c r="F103" t="s">
-        <v>19</v>
-      </c>
-      <c r="I103" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>8</v>
-      </c>
-      <c r="C104" s="1">
-        <v>45776</v>
-      </c>
-      <c r="D104" t="s">
-        <v>9</v>
-      </c>
-      <c r="F104" t="s">
-        <v>72</v>
-      </c>
-      <c r="I104" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>8</v>
-      </c>
-      <c r="C105" s="1">
-        <v>45763</v>
-      </c>
-      <c r="D105" t="s">
-        <v>9</v>
-      </c>
-      <c r="F105" t="s">
-        <v>131</v>
-      </c>
       <c r="I105" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>8</v>
       </c>
       <c r="C106" s="1">
-        <v>45756</v>
+        <v>45807</v>
       </c>
       <c r="D106" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="F106" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="I106" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>8</v>
       </c>
       <c r="C107" s="1">
-        <v>45756</v>
+        <v>45810</v>
       </c>
       <c r="D107" t="s">
-        <v>133</v>
-      </c>
-      <c r="F107" t="s">
-        <v>136</v>
-      </c>
-      <c r="I107" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>8</v>
       </c>
       <c r="C108" s="1">
-        <v>45868</v>
+        <v>45811</v>
       </c>
       <c r="D108" t="s">
         <v>16</v>
       </c>
       <c r="F108" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I108" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>8</v>
       </c>
       <c r="C109" s="1">
-        <v>45868</v>
+        <v>45811</v>
       </c>
       <c r="D109" t="s">
         <v>16</v>
       </c>
       <c r="F109" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I109" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110" s="1">
-        <v>45868</v>
-      </c>
-      <c r="D110" t="s">
-        <v>9</v>
-      </c>
-      <c r="F110" t="s">
-        <v>72</v>
-      </c>
-      <c r="I110" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" s="2"/>
+      <c r="C110" s="3">
+        <v>45813</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>8</v>
       </c>
       <c r="C111" s="1">
-        <v>45860</v>
+        <v>45814</v>
       </c>
       <c r="D111" t="s">
         <v>16</v>
@@ -3606,15 +3607,15 @@
         <v>35</v>
       </c>
       <c r="I111" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>8</v>
       </c>
       <c r="C112" s="1">
-        <v>45860</v>
+        <v>45814</v>
       </c>
       <c r="D112" t="s">
         <v>16</v>
@@ -3623,7 +3624,7 @@
         <v>37</v>
       </c>
       <c r="I112" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -3631,33 +3632,36 @@
         <v>8</v>
       </c>
       <c r="C113" s="1">
-        <v>45859</v>
+        <v>45824</v>
       </c>
       <c r="D113" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="F113" t="s">
+        <v>149</v>
       </c>
       <c r="I113" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>8</v>
       </c>
       <c r="C114" s="1">
-        <v>45854</v>
+        <v>45835</v>
       </c>
       <c r="D114" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F114" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="I114" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>8</v>
       </c>
@@ -3668,13 +3672,13 @@
         <v>16</v>
       </c>
       <c r="F115" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I115" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -3682,55 +3686,52 @@
         <v>45835</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F116" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="I116" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>8</v>
       </c>
       <c r="C117" s="1">
-        <v>45835</v>
+        <v>45854</v>
       </c>
       <c r="D117" t="s">
         <v>9</v>
       </c>
       <c r="F117" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="I117" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>8</v>
       </c>
       <c r="C118" s="1">
-        <v>45824</v>
+        <v>45859</v>
       </c>
       <c r="D118" t="s">
-        <v>9</v>
-      </c>
-      <c r="F118" t="s">
-        <v>149</v>
+        <v>12</v>
       </c>
       <c r="I118" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>8</v>
       </c>
       <c r="C119" s="1">
-        <v>45814</v>
+        <v>45860</v>
       </c>
       <c r="D119" t="s">
         <v>16</v>
@@ -3739,15 +3740,15 @@
         <v>35</v>
       </c>
       <c r="I119" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>8</v>
       </c>
       <c r="C120" s="1">
-        <v>45814</v>
+        <v>45860</v>
       </c>
       <c r="D120" t="s">
         <v>16</v>
@@ -3756,137 +3757,141 @@
         <v>37</v>
       </c>
       <c r="I120" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C121" s="3">
-        <v>45813</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I121" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121"/>
+      <c r="C121" s="1">
+        <v>45868</v>
+      </c>
+      <c r="D121" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121"/>
+      <c r="F121" t="s">
+        <v>17</v>
+      </c>
+      <c r="G121"/>
+      <c r="H121"/>
+      <c r="I121" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>8</v>
       </c>
       <c r="C122" s="1">
-        <v>45811</v>
+        <v>45868</v>
       </c>
       <c r="D122" t="s">
         <v>16</v>
       </c>
       <c r="F122" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I122" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>8</v>
       </c>
       <c r="C123" s="1">
-        <v>45811</v>
+        <v>45868</v>
       </c>
       <c r="D123" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F123" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="I123" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>8</v>
       </c>
       <c r="C124" s="1">
-        <v>45926</v>
+        <v>45873</v>
       </c>
       <c r="D124" t="s">
         <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I124" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>8</v>
       </c>
       <c r="C125" s="1">
-        <v>45926</v>
+        <v>45873</v>
       </c>
       <c r="D125" t="s">
         <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I125" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>8</v>
       </c>
       <c r="C126" s="1">
-        <v>45925</v>
+        <v>45873</v>
       </c>
       <c r="D126" t="s">
-        <v>12</v>
-      </c>
-      <c r="I126" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F126" t="s">
+        <v>87</v>
+      </c>
+      <c r="I126" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>8</v>
       </c>
       <c r="C127" s="1">
-        <v>45923</v>
+        <v>45881</v>
       </c>
       <c r="D127" t="s">
-        <v>16</v>
-      </c>
-      <c r="F127" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="I127" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>8</v>
       </c>
       <c r="C128" s="1">
-        <v>45923</v>
+        <v>45881</v>
       </c>
       <c r="D128" t="s">
-        <v>16</v>
-      </c>
-      <c r="F128" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="I128" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -3894,13 +3899,16 @@
         <v>8</v>
       </c>
       <c r="C129" s="1">
-        <v>45922</v>
+        <v>45882</v>
       </c>
       <c r="D129" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F129" t="s">
+        <v>17</v>
       </c>
       <c r="I129" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -3908,115 +3916,118 @@
         <v>8</v>
       </c>
       <c r="C130" s="1">
-        <v>45922</v>
+        <v>45882</v>
       </c>
       <c r="D130" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F130" t="s">
+        <v>19</v>
       </c>
       <c r="I130" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>8</v>
       </c>
       <c r="C131" s="1">
-        <v>45919</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F131" t="s">
+        <v>182</v>
+      </c>
+      <c r="I131" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132" s="1">
+        <v>45905</v>
+      </c>
+      <c r="D132" t="s">
+        <v>12</v>
+      </c>
+      <c r="H132" t="s">
+        <v>278</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" s="1">
+        <v>45908</v>
+      </c>
+      <c r="D133" t="s">
+        <v>16</v>
+      </c>
+      <c r="F133" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" s="1">
+        <v>45908</v>
+      </c>
+      <c r="D134" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134" t="s">
         <v>19</v>
       </c>
-      <c r="I131" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>8</v>
-      </c>
-      <c r="C132" s="1">
-        <v>45919</v>
-      </c>
-      <c r="D132" t="s">
-        <v>16</v>
-      </c>
-      <c r="F132" t="s">
-        <v>17</v>
-      </c>
-      <c r="I132" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>8</v>
-      </c>
-      <c r="C133" s="1">
-        <v>45919</v>
-      </c>
-      <c r="D133" t="s">
-        <v>16</v>
-      </c>
-      <c r="F133" t="s">
-        <v>87</v>
-      </c>
-      <c r="I133" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>8</v>
-      </c>
-      <c r="C134" s="1">
-        <v>45917</v>
-      </c>
-      <c r="D134" t="s">
-        <v>16</v>
-      </c>
-      <c r="F134" t="s">
-        <v>17</v>
-      </c>
       <c r="I134" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>8</v>
       </c>
       <c r="C135" s="1">
-        <v>45917</v>
+        <v>45910</v>
       </c>
       <c r="D135" t="s">
-        <v>16</v>
-      </c>
-      <c r="F135" t="s">
-        <v>19</v>
-      </c>
-      <c r="I135" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H135" t="s">
+        <v>278</v>
+      </c>
+      <c r="I135" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>8</v>
       </c>
       <c r="C136" s="1">
-        <v>45916</v>
+        <v>45911</v>
       </c>
       <c r="D136" t="s">
-        <v>12</v>
-      </c>
-      <c r="H136" t="s">
-        <v>278</v>
-      </c>
-      <c r="I136" s="5" t="s">
-        <v>168</v>
+        <v>16</v>
+      </c>
+      <c r="F136" t="s">
+        <v>35</v>
+      </c>
+      <c r="I136" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
@@ -4024,33 +4035,36 @@
         <v>8</v>
       </c>
       <c r="C137" s="1">
-        <v>45916</v>
+        <v>45911</v>
       </c>
       <c r="D137" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F137" t="s">
+        <v>37</v>
       </c>
       <c r="I137" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>8</v>
       </c>
       <c r="C138" s="1">
-        <v>45916</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="F138" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I138" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -4061,103 +4075,100 @@
         <v>133</v>
       </c>
       <c r="F139" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I139" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>8</v>
       </c>
       <c r="C140" s="1">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="D140" t="s">
-        <v>133</v>
-      </c>
-      <c r="F140" t="s">
-        <v>174</v>
-      </c>
-      <c r="I140" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H140" t="s">
+        <v>278</v>
+      </c>
+      <c r="I140" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>8</v>
       </c>
       <c r="C141" s="1">
-        <v>45911</v>
+        <v>45916</v>
       </c>
       <c r="D141" t="s">
-        <v>16</v>
-      </c>
-      <c r="F141" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="I141" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>8</v>
       </c>
       <c r="C142" s="1">
-        <v>45911</v>
+        <v>45916</v>
       </c>
       <c r="D142" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F142" t="s">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="I142" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>8</v>
       </c>
       <c r="C143" s="1">
-        <v>45910</v>
+        <v>45917</v>
       </c>
       <c r="D143" t="s">
-        <v>12</v>
-      </c>
-      <c r="H143" t="s">
-        <v>278</v>
-      </c>
-      <c r="I143" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>8</v>
       </c>
       <c r="C144" s="1">
-        <v>45908</v>
+        <v>45917</v>
       </c>
       <c r="D144" t="s">
         <v>16</v>
       </c>
       <c r="F144" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I144" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>8</v>
       </c>
       <c r="C145" s="1">
-        <v>45908</v>
+        <v>45919</v>
       </c>
       <c r="D145" t="s">
         <v>16</v>
@@ -4166,75 +4177,69 @@
         <v>19</v>
       </c>
       <c r="I145" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>8</v>
       </c>
       <c r="C146" s="1">
-        <v>45905</v>
+        <v>45919</v>
       </c>
       <c r="D146" t="s">
-        <v>12</v>
-      </c>
-      <c r="H146" t="s">
-        <v>278</v>
-      </c>
-      <c r="I146" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>8</v>
       </c>
       <c r="C147" s="1">
-        <v>45887</v>
+        <v>45919</v>
       </c>
       <c r="D147" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F147" t="s">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="I147" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>8</v>
       </c>
       <c r="C148" s="1">
-        <v>45882</v>
+        <v>45922</v>
       </c>
       <c r="D148" t="s">
-        <v>16</v>
-      </c>
-      <c r="F148" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I148" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>8</v>
       </c>
       <c r="C149" s="1">
-        <v>45882</v>
+        <v>45922</v>
       </c>
       <c r="D149" t="s">
-        <v>16</v>
-      </c>
-      <c r="F149" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I149" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -4242,13 +4247,16 @@
         <v>8</v>
       </c>
       <c r="C150" s="1">
-        <v>45881</v>
+        <v>45923</v>
       </c>
       <c r="D150" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F150" t="s">
+        <v>35</v>
       </c>
       <c r="I150" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -4256,149 +4264,143 @@
         <v>8</v>
       </c>
       <c r="C151" s="1">
-        <v>45881</v>
+        <v>45923</v>
       </c>
       <c r="D151" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F151" t="s">
+        <v>37</v>
       </c>
       <c r="I151" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>8</v>
       </c>
       <c r="C152" s="1">
-        <v>45873</v>
+        <v>45925</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
-      </c>
-      <c r="F152" t="s">
+        <v>12</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>8</v>
+      </c>
+      <c r="C153" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D153" t="s">
+        <v>16</v>
+      </c>
+      <c r="F153" t="s">
+        <v>35</v>
+      </c>
+      <c r="I153" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>8</v>
+      </c>
+      <c r="C154" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D154" t="s">
+        <v>16</v>
+      </c>
+      <c r="F154" t="s">
+        <v>37</v>
+      </c>
+      <c r="I154" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>8</v>
+      </c>
+      <c r="C155" s="1">
+        <v>45938</v>
+      </c>
+      <c r="D155" t="s">
+        <v>12</v>
+      </c>
+      <c r="I155" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>8</v>
+      </c>
+      <c r="C156" s="1">
+        <v>45939</v>
+      </c>
+      <c r="D156" t="s">
+        <v>16</v>
+      </c>
+      <c r="F156" t="s">
         <v>17</v>
       </c>
-      <c r="I152" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>8</v>
-      </c>
-      <c r="C153" s="1">
-        <v>45873</v>
-      </c>
-      <c r="D153" t="s">
-        <v>16</v>
-      </c>
-      <c r="F153" t="s">
+      <c r="I156" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="C157" s="1">
+        <v>45939</v>
+      </c>
+      <c r="D157" t="s">
+        <v>16</v>
+      </c>
+      <c r="F157" t="s">
         <v>19</v>
       </c>
-      <c r="I153" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>8</v>
-      </c>
-      <c r="C154" s="1">
-        <v>45873</v>
-      </c>
-      <c r="D154" t="s">
-        <v>16</v>
-      </c>
-      <c r="F154" t="s">
-        <v>87</v>
-      </c>
-      <c r="I154" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>8</v>
-      </c>
-      <c r="C155" s="1">
-        <v>45982</v>
-      </c>
-      <c r="D155" t="s">
-        <v>16</v>
-      </c>
-      <c r="F155" t="s">
+      <c r="I157" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>8</v>
+      </c>
+      <c r="C158" s="1">
+        <v>45944</v>
+      </c>
+      <c r="D158" t="s">
+        <v>12</v>
+      </c>
+      <c r="I158" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>8</v>
+      </c>
+      <c r="C159" s="1">
+        <v>45945</v>
+      </c>
+      <c r="D159" t="s">
+        <v>16</v>
+      </c>
+      <c r="F159" t="s">
         <v>17</v>
       </c>
-      <c r="I155" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>8</v>
-      </c>
-      <c r="C156" s="1">
-        <v>45982</v>
-      </c>
-      <c r="D156" t="s">
-        <v>16</v>
-      </c>
-      <c r="F156" t="s">
-        <v>19</v>
-      </c>
-      <c r="I156" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>8</v>
-      </c>
-      <c r="C157" s="1">
-        <v>45981</v>
-      </c>
-      <c r="D157" t="s">
-        <v>12</v>
-      </c>
-      <c r="H157" t="s">
-        <v>278</v>
-      </c>
-      <c r="I157" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>8</v>
-      </c>
-      <c r="C158" s="1">
-        <v>45979</v>
-      </c>
-      <c r="D158" t="s">
-        <v>16</v>
-      </c>
-      <c r="F158" t="s">
-        <v>17</v>
-      </c>
-      <c r="I158" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>8</v>
-      </c>
-      <c r="C159" s="1">
-        <v>45979</v>
-      </c>
-      <c r="D159" t="s">
-        <v>16</v>
-      </c>
-      <c r="F159" t="s">
-        <v>19</v>
-      </c>
       <c r="I159" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -4406,101 +4408,101 @@
         <v>8</v>
       </c>
       <c r="C160" s="1">
-        <v>45978</v>
+        <v>45945</v>
       </c>
       <c r="D160" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F160" t="s">
+        <v>19</v>
       </c>
       <c r="I160" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>8</v>
       </c>
       <c r="C161" s="1">
-        <v>45978</v>
+        <v>45946</v>
       </c>
       <c r="D161" t="s">
         <v>9</v>
       </c>
       <c r="F161" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="I161" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>8</v>
       </c>
       <c r="C162" s="1">
-        <v>45960</v>
+        <v>45952</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
-      </c>
-      <c r="F162" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I162" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>8</v>
       </c>
       <c r="C163" s="1">
-        <v>45960</v>
+        <v>45953</v>
       </c>
       <c r="D163" t="s">
         <v>16</v>
       </c>
       <c r="F163" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I163" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>8</v>
       </c>
       <c r="C164" s="1">
-        <v>45960</v>
+        <v>45953</v>
       </c>
       <c r="D164" t="s">
         <v>16</v>
       </c>
       <c r="F164" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="I164" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>8</v>
       </c>
       <c r="C165" s="1">
-        <v>45958</v>
+        <v>45957</v>
       </c>
       <c r="D165" t="s">
-        <v>16</v>
-      </c>
-      <c r="F165" t="s">
-        <v>35</v>
-      </c>
-      <c r="I165" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H165" t="s">
+        <v>278</v>
+      </c>
+      <c r="I165" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>8</v>
       </c>
@@ -4511,61 +4513,61 @@
         <v>16</v>
       </c>
       <c r="F166" t="s">
+        <v>35</v>
+      </c>
+      <c r="I166" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>8</v>
+      </c>
+      <c r="C167" s="1">
+        <v>45958</v>
+      </c>
+      <c r="D167" t="s">
+        <v>16</v>
+      </c>
+      <c r="F167" t="s">
         <v>37</v>
       </c>
-      <c r="I166" t="s">
+      <c r="I167" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>8</v>
-      </c>
-      <c r="C167" s="1">
-        <v>45957</v>
-      </c>
-      <c r="D167" t="s">
-        <v>12</v>
-      </c>
-      <c r="H167" t="s">
-        <v>278</v>
-      </c>
-      <c r="I167" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>8</v>
       </c>
       <c r="C168" s="1">
-        <v>45953</v>
+        <v>45960</v>
       </c>
       <c r="D168" t="s">
         <v>16</v>
       </c>
       <c r="F168" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I168" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>8</v>
       </c>
       <c r="C169" s="1">
-        <v>45953</v>
+        <v>45960</v>
       </c>
       <c r="D169" t="s">
         <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I169" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -4573,64 +4575,64 @@
         <v>8</v>
       </c>
       <c r="C170" s="1">
-        <v>45952</v>
+        <v>45960</v>
       </c>
       <c r="D170" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F170" t="s">
+        <v>87</v>
       </c>
       <c r="I170" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>8</v>
       </c>
       <c r="C171" s="1">
-        <v>45946</v>
+        <v>45978</v>
       </c>
       <c r="D171" t="s">
+        <v>12</v>
+      </c>
+      <c r="I171" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="C172" s="1">
+        <v>45978</v>
+      </c>
+      <c r="D172" t="s">
         <v>9</v>
       </c>
-      <c r="F171" t="s">
-        <v>208</v>
-      </c>
-      <c r="I171" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>8</v>
-      </c>
-      <c r="C172" s="1">
-        <v>45945</v>
-      </c>
-      <c r="D172" t="s">
-        <v>16</v>
-      </c>
       <c r="F172" t="s">
+        <v>197</v>
+      </c>
+      <c r="I172" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>8</v>
+      </c>
+      <c r="C173" s="1">
+        <v>45979</v>
+      </c>
+      <c r="D173" t="s">
+        <v>16</v>
+      </c>
+      <c r="F173" t="s">
         <v>17</v>
       </c>
-      <c r="I172" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>8</v>
-      </c>
-      <c r="C173" s="1">
-        <v>45945</v>
-      </c>
-      <c r="D173" t="s">
-        <v>16</v>
-      </c>
-      <c r="F173" t="s">
-        <v>19</v>
-      </c>
       <c r="I173" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
@@ -4638,95 +4640,95 @@
         <v>8</v>
       </c>
       <c r="C174" s="1">
-        <v>45944</v>
+        <v>45979</v>
       </c>
       <c r="D174" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F174" t="s">
+        <v>19</v>
       </c>
       <c r="I174" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>8</v>
       </c>
       <c r="C175" s="1">
-        <v>45939</v>
+        <v>45981</v>
       </c>
       <c r="D175" t="s">
-        <v>16</v>
-      </c>
-      <c r="F175" t="s">
+        <v>12</v>
+      </c>
+      <c r="H175" t="s">
+        <v>278</v>
+      </c>
+      <c r="I175" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176" s="1">
+        <v>45982</v>
+      </c>
+      <c r="D176" t="s">
+        <v>16</v>
+      </c>
+      <c r="F176" t="s">
         <v>17</v>
       </c>
-      <c r="I175" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>8</v>
-      </c>
-      <c r="C176" s="1">
-        <v>45939</v>
-      </c>
-      <c r="D176" t="s">
-        <v>16</v>
-      </c>
-      <c r="F176" t="s">
+      <c r="I176" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="C177" s="1">
+        <v>45982</v>
+      </c>
+      <c r="D177" t="s">
+        <v>16</v>
+      </c>
+      <c r="F177" t="s">
         <v>19</v>
       </c>
-      <c r="I176" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>8</v>
-      </c>
-      <c r="C177" s="1">
-        <v>45938</v>
-      </c>
-      <c r="D177" t="s">
-        <v>12</v>
-      </c>
-      <c r="I177" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I177" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>8</v>
       </c>
       <c r="C178" s="1">
-        <v>46049</v>
+        <v>45993</v>
       </c>
       <c r="D178" t="s">
-        <v>16</v>
-      </c>
-      <c r="F178" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I178" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>8</v>
       </c>
       <c r="C179" s="1">
-        <v>46049</v>
+        <v>45993</v>
       </c>
       <c r="D179" t="s">
-        <v>16</v>
-      </c>
-      <c r="F179" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I179" t="s">
-        <v>217</v>
+        <v>269</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
@@ -4734,21 +4736,21 @@
         <v>8</v>
       </c>
       <c r="C180" s="1">
-        <v>46048</v>
+        <v>45994</v>
       </c>
       <c r="D180" t="s">
         <v>12</v>
       </c>
       <c r="I180" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>8</v>
       </c>
       <c r="C181" s="1">
-        <v>46044</v>
+        <v>45994</v>
       </c>
       <c r="D181" t="s">
         <v>16</v>
@@ -4757,15 +4759,15 @@
         <v>35</v>
       </c>
       <c r="I181" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>8</v>
       </c>
       <c r="C182" s="1">
-        <v>46044</v>
+        <v>45994</v>
       </c>
       <c r="D182" t="s">
         <v>16</v>
@@ -4774,7 +4776,7 @@
         <v>37</v>
       </c>
       <c r="I182" t="s">
-        <v>220</v>
+        <v>267</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
@@ -4782,13 +4784,13 @@
         <v>8</v>
       </c>
       <c r="C183" s="1">
-        <v>46043</v>
+        <v>45995</v>
       </c>
       <c r="D183" t="s">
         <v>12</v>
       </c>
       <c r="I183" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -4796,13 +4798,16 @@
         <v>8</v>
       </c>
       <c r="C184" s="1">
-        <v>46043</v>
+        <v>45995</v>
       </c>
       <c r="D184" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F184" t="s">
+        <v>35</v>
       </c>
       <c r="I184" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -4810,13 +4815,16 @@
         <v>8</v>
       </c>
       <c r="C185" s="1">
-        <v>46043</v>
+        <v>45995</v>
       </c>
       <c r="D185" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F185" t="s">
+        <v>37</v>
       </c>
       <c r="I185" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
@@ -4824,13 +4832,16 @@
         <v>8</v>
       </c>
       <c r="C186" s="1">
-        <v>46043</v>
+        <v>45996</v>
       </c>
       <c r="D186" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F186" t="s">
+        <v>17</v>
       </c>
       <c r="I186" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
@@ -4838,47 +4849,47 @@
         <v>8</v>
       </c>
       <c r="C187" s="1">
-        <v>46043</v>
+        <v>45996</v>
       </c>
       <c r="D187" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F187" t="s">
+        <v>19</v>
       </c>
       <c r="I187" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>8</v>
       </c>
       <c r="C188" s="1">
-        <v>46043</v>
+        <v>45999</v>
       </c>
       <c r="D188" t="s">
-        <v>16</v>
-      </c>
-      <c r="F188" t="s">
+        <v>12</v>
+      </c>
+      <c r="I188" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>8</v>
+      </c>
+      <c r="C189" s="1">
+        <v>46000</v>
+      </c>
+      <c r="D189" t="s">
+        <v>16</v>
+      </c>
+      <c r="F189" t="s">
         <v>35</v>
       </c>
-      <c r="I188" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>8</v>
-      </c>
-      <c r="C189" s="1">
-        <v>46043</v>
-      </c>
-      <c r="D189" t="s">
-        <v>16</v>
-      </c>
-      <c r="F189" t="s">
-        <v>37</v>
-      </c>
       <c r="I189" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -4886,86 +4897,83 @@
         <v>8</v>
       </c>
       <c r="C190" s="1">
-        <v>46042</v>
+        <v>46000</v>
       </c>
       <c r="D190" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F190" t="s">
+        <v>37</v>
       </c>
       <c r="I190" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>8</v>
       </c>
       <c r="C191" s="1">
-        <v>46042</v>
+        <v>46007</v>
       </c>
       <c r="D191" t="s">
         <v>12</v>
       </c>
-      <c r="I191" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I191" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>8</v>
       </c>
       <c r="C192" s="1">
-        <v>46038</v>
+        <v>46007</v>
       </c>
       <c r="D192" t="s">
+        <v>12</v>
+      </c>
+      <c r="I192" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>8</v>
+      </c>
+      <c r="C193" s="1">
+        <v>46007</v>
+      </c>
+      <c r="D193" t="s">
         <v>9</v>
       </c>
-      <c r="F192" t="s">
-        <v>230</v>
-      </c>
-      <c r="I192" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>8</v>
-      </c>
-      <c r="C193" s="1">
-        <v>46029</v>
-      </c>
-      <c r="D193" t="s">
-        <v>16</v>
-      </c>
       <c r="F193" t="s">
-        <v>35</v>
+        <v>255</v>
       </c>
       <c r="I193" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>8</v>
       </c>
       <c r="C194" s="1">
-        <v>46029</v>
+        <v>46008</v>
       </c>
       <c r="D194" t="s">
-        <v>16</v>
-      </c>
-      <c r="F194" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="I194" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>8</v>
       </c>
       <c r="C195" s="1">
-        <v>46028</v>
+        <v>46008</v>
       </c>
       <c r="D195" t="s">
         <v>16</v>
@@ -4974,15 +4982,15 @@
         <v>17</v>
       </c>
       <c r="I195" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>8</v>
       </c>
       <c r="C196" s="1">
-        <v>46028</v>
+        <v>46008</v>
       </c>
       <c r="D196" t="s">
         <v>16</v>
@@ -4991,7 +4999,7 @@
         <v>19</v>
       </c>
       <c r="I196" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -4999,64 +5007,64 @@
         <v>8</v>
       </c>
       <c r="C197" s="1">
-        <v>46028</v>
+        <v>46009</v>
       </c>
       <c r="D197" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F197" t="s">
+        <v>17</v>
       </c>
       <c r="I197" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>8</v>
       </c>
       <c r="C198" s="1">
-        <v>46028</v>
+        <v>46009</v>
       </c>
       <c r="D198" t="s">
         <v>16</v>
       </c>
       <c r="F198" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="I198" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>8</v>
       </c>
       <c r="C199" s="1">
-        <v>46028</v>
+        <v>46010</v>
       </c>
       <c r="D199" t="s">
-        <v>16</v>
-      </c>
-      <c r="F199" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I199" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>8</v>
       </c>
       <c r="C200" s="1">
-        <v>46028</v>
+        <v>46013</v>
       </c>
       <c r="D200" t="s">
         <v>16</v>
       </c>
       <c r="F200" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I200" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -5064,47 +5072,44 @@
         <v>8</v>
       </c>
       <c r="C201" s="1">
-        <v>46027</v>
+        <v>46013</v>
       </c>
       <c r="D201" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F201" t="s">
+        <v>37</v>
       </c>
       <c r="I201" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>8</v>
       </c>
       <c r="C202" s="1">
-        <v>46017</v>
+        <v>46015</v>
       </c>
       <c r="D202" t="s">
-        <v>16</v>
-      </c>
-      <c r="F202" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I202" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>8</v>
       </c>
       <c r="C203" s="1">
-        <v>46017</v>
+        <v>46015</v>
       </c>
       <c r="D203" t="s">
-        <v>16</v>
-      </c>
-      <c r="F203" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I203" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -5112,13 +5117,16 @@
         <v>8</v>
       </c>
       <c r="C204" s="1">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="D204" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F204" t="s">
+        <v>17</v>
       </c>
       <c r="I204" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
@@ -5126,47 +5134,47 @@
         <v>8</v>
       </c>
       <c r="C205" s="1">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="D205" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F205" t="s">
+        <v>19</v>
       </c>
       <c r="I205" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>8</v>
       </c>
       <c r="C206" s="1">
-        <v>46013</v>
+        <v>46027</v>
       </c>
       <c r="D206" t="s">
-        <v>16</v>
-      </c>
-      <c r="F206" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="I206" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>8</v>
       </c>
       <c r="C207" s="1">
-        <v>46013</v>
+        <v>46028</v>
       </c>
       <c r="D207" t="s">
         <v>16</v>
       </c>
       <c r="F207" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I207" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
@@ -5174,47 +5182,47 @@
         <v>8</v>
       </c>
       <c r="C208" s="1">
-        <v>46010</v>
+        <v>46028</v>
       </c>
       <c r="D208" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F208" t="s">
+        <v>19</v>
       </c>
       <c r="I208" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>8</v>
       </c>
       <c r="C209" s="1">
-        <v>46009</v>
+        <v>46028</v>
       </c>
       <c r="D209" t="s">
-        <v>16</v>
-      </c>
-      <c r="F209" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I209" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>8</v>
       </c>
       <c r="C210" s="1">
-        <v>46009</v>
+        <v>46028</v>
       </c>
       <c r="D210" t="s">
         <v>16</v>
       </c>
       <c r="F210" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="I210" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -5222,61 +5230,67 @@
         <v>8</v>
       </c>
       <c r="C211" s="1">
-        <v>46008</v>
+        <v>46028</v>
       </c>
       <c r="D211" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F211" t="s">
+        <v>17</v>
       </c>
       <c r="I211" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>8</v>
       </c>
       <c r="C212" s="1">
-        <v>46008</v>
+        <v>46028</v>
       </c>
       <c r="D212" t="s">
         <v>16</v>
       </c>
       <c r="F212" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I212" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>8</v>
       </c>
       <c r="C213" s="1">
-        <v>46008</v>
+        <v>46029</v>
       </c>
       <c r="D213" t="s">
         <v>16</v>
       </c>
       <c r="F213" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I213" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>8</v>
       </c>
       <c r="C214" s="1">
-        <v>46007</v>
+        <v>46029</v>
       </c>
       <c r="D214" t="s">
-        <v>12</v>
-      </c>
-      <c r="I214" s="4" t="s">
-        <v>253</v>
+        <v>16</v>
+      </c>
+      <c r="F214" t="s">
+        <v>37</v>
+      </c>
+      <c r="I214" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -5284,64 +5298,58 @@
         <v>8</v>
       </c>
       <c r="C215" s="1">
-        <v>46007</v>
+        <v>46038</v>
       </c>
       <c r="D215" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="F215" t="s">
+        <v>230</v>
       </c>
       <c r="I215" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>8</v>
       </c>
       <c r="C216" s="1">
-        <v>46007</v>
+        <v>46042</v>
       </c>
       <c r="D216" t="s">
-        <v>9</v>
-      </c>
-      <c r="F216" t="s">
-        <v>255</v>
+        <v>12</v>
       </c>
       <c r="I216" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>8</v>
       </c>
       <c r="C217" s="1">
-        <v>46000</v>
+        <v>46042</v>
       </c>
       <c r="D217" t="s">
-        <v>16</v>
-      </c>
-      <c r="F217" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="I217" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>8</v>
       </c>
       <c r="C218" s="1">
-        <v>46000</v>
+        <v>46043</v>
       </c>
       <c r="D218" t="s">
-        <v>16</v>
-      </c>
-      <c r="F218" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="I218" t="s">
-        <v>258</v>
+        <v>221</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
@@ -5349,47 +5357,41 @@
         <v>8</v>
       </c>
       <c r="C219" s="1">
-        <v>45999</v>
+        <v>46043</v>
       </c>
       <c r="D219" t="s">
         <v>12</v>
       </c>
       <c r="I219" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>8</v>
       </c>
       <c r="C220" s="1">
-        <v>45996</v>
+        <v>46043</v>
       </c>
       <c r="D220" t="s">
-        <v>16</v>
-      </c>
-      <c r="F220" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I220" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>8</v>
       </c>
       <c r="C221" s="1">
-        <v>45996</v>
+        <v>46043</v>
       </c>
       <c r="D221" t="s">
-        <v>16</v>
-      </c>
-      <c r="F221" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I221" t="s">
-        <v>261</v>
+        <v>224</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -5397,21 +5399,21 @@
         <v>8</v>
       </c>
       <c r="C222" s="1">
-        <v>45995</v>
+        <v>46043</v>
       </c>
       <c r="D222" t="s">
         <v>12</v>
       </c>
       <c r="I222" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>8</v>
       </c>
       <c r="C223" s="1">
-        <v>45995</v>
+        <v>46043</v>
       </c>
       <c r="D223" t="s">
         <v>16</v>
@@ -5420,15 +5422,15 @@
         <v>35</v>
       </c>
       <c r="I223" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>8</v>
       </c>
       <c r="C224" s="1">
-        <v>45995</v>
+        <v>46043</v>
       </c>
       <c r="D224" t="s">
         <v>16</v>
@@ -5437,7 +5439,7 @@
         <v>37</v>
       </c>
       <c r="I224" t="s">
-        <v>264</v>
+        <v>227</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -5445,47 +5447,47 @@
         <v>8</v>
       </c>
       <c r="C225" s="1">
-        <v>45994</v>
+        <v>46044</v>
       </c>
       <c r="D225" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F225" t="s">
+        <v>35</v>
       </c>
       <c r="I225" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>8</v>
       </c>
       <c r="C226" s="1">
-        <v>45994</v>
+        <v>46044</v>
       </c>
       <c r="D226" t="s">
         <v>16</v>
       </c>
       <c r="F226" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I226" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>8</v>
       </c>
       <c r="C227" s="1">
-        <v>45994</v>
+        <v>46048</v>
       </c>
       <c r="D227" t="s">
-        <v>16</v>
-      </c>
-      <c r="F227" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="I227" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
@@ -5493,13 +5495,16 @@
         <v>8</v>
       </c>
       <c r="C228" s="1">
-        <v>45993</v>
+        <v>46049</v>
       </c>
       <c r="D228" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F228" t="s">
+        <v>17</v>
       </c>
       <c r="I228" t="s">
-        <v>268</v>
+        <v>216</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
@@ -5507,13 +5512,16 @@
         <v>8</v>
       </c>
       <c r="C229" s="1">
-        <v>45993</v>
+        <v>46049</v>
       </c>
       <c r="D229" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F229" t="s">
+        <v>19</v>
       </c>
       <c r="I229" t="s">
-        <v>269</v>
+        <v>217</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
@@ -5521,47 +5529,44 @@
         <v>8</v>
       </c>
       <c r="C230" s="1">
-        <v>46056</v>
+        <v>46052</v>
       </c>
       <c r="D230" t="s">
         <v>12</v>
       </c>
       <c r="I230" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>8</v>
       </c>
       <c r="C231" s="1">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="D231" t="s">
-        <v>16</v>
-      </c>
-      <c r="F231" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="I231" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>8</v>
       </c>
       <c r="C232" s="1">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="D232" t="s">
         <v>16</v>
       </c>
       <c r="F232" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I232" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
@@ -5572,44 +5577,44 @@
         <v>46055</v>
       </c>
       <c r="D233" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F233" t="s">
+        <v>19</v>
       </c>
       <c r="I233" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>8</v>
       </c>
       <c r="C234" s="1">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="D234" t="s">
-        <v>16</v>
-      </c>
-      <c r="F234" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I234" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>8</v>
       </c>
       <c r="C235" s="1">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="D235" t="s">
         <v>16</v>
       </c>
       <c r="F235" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I235" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
@@ -5617,23 +5622,23 @@
         <v>8</v>
       </c>
       <c r="C236" s="1">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="D236" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="F236" t="s">
+        <v>37</v>
       </c>
       <c r="I236" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I236" xr:uid="{D08F2675-AFF5-4BC4-8A45-9611FEC249CE}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="TRADE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I236" xr:uid="{D08F2675-AFF5-4BC4-8A45-9611FEC249CE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I236">
+    <sortCondition ref="C2:C236"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>